--- a/입력양식.xlsx
+++ b/입력양식.xlsx
@@ -433,17 +433,12 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>1 오래된 순서부터 4까지</t>
+        <t>3년 이상 / 1~3년 / 6개월~1년 / 6개월 미만 중에서 고릅니다</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>3년 이상 / 1~3년 / 6개월~1년 / 6개월 미만</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>그 구간 인원</t>
+        <t>그 구간 인원. 0명이어도 0 으로 넣으세요</t>
       </text>
     </comment>
   </commentList>
@@ -473,12 +468,12 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>0h / 1-10 / 11-20 / 21-30 / 30h+ 중 하나</t>
+        <t>그 사람의 한 달 초과근무 시간. 34시간이면 34</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>그 구간에 해당하는 인원. 0명인 칸은 넣지 않아도 됩니다</t>
+        <t>같은 시간을 일한 인원 수. 보통 1</t>
       </text>
     </comment>
   </commentList>
@@ -648,27 +643,22 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>2 견적 · 3 협상 · 4 계약 (문의는 넣지 않음)</t>
+        <t>견적 / 협상 / 계약 중에서 고릅니다. 문의는 넣지 않습니다</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>견적 / 협상 / 계약</t>
+        <t>그 단계 건수</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>그 단계 건수</t>
+        <t>그 단계 예상 계약금액 (만원)</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>그 단계 예상 계약금액 (만원)</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>계약 단계에만 씁니다. 나머지는 빈칸</t>
+        <t>계약 단계에만 씁니다. 견적·협상은 빈칸</t>
       </text>
     </comment>
   </commentList>
@@ -918,7 +908,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>가입한 연도</t>
+        <t>가입한 연도. 이 사람들이 처음 온 해</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -928,12 +918,17 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>0 이면 가입한 달, 1 이면 한 달 뒤</t>
+        <t>확인하는 시점의 연도</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>그때 남아 있는 인원</t>
+        <t>확인하는 시점의 월</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>그때 남아 있는 인원. 3월에 온 사람들이 7월에 몇 명 남았나</t>
       </text>
     </comment>
   </commentList>
@@ -1539,9 +1534,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="B53" t="inlineStr"/>
-    </row>
+    <row r="53" ht="17" customHeight="1"/>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="15" t="n"/>
       <c r="B54" s="16" t="inlineStr">
@@ -2553,13 +2546,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2575,10 +2569,15 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>m_index</t>
+          <t>year</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>retained</t>
         </is>
@@ -2592,12 +2591,15 @@
         <v>3</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>4</v>
+        <v>2026</v>
       </c>
       <c r="D2" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>168</v>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>← 이 줄은 예시입니다. CSV로 저장하기 전에 2행 전체를 지우세요.</t>
         </is>
@@ -2608,342 +2610,399 @@
       <c r="B3" s="10" t="n"/>
       <c r="C3" s="10" t="n"/>
       <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="n"/>
       <c r="B4" s="10" t="n"/>
       <c r="C4" s="10" t="n"/>
       <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="n"/>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="10" t="n"/>
       <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n"/>
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n"/>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n"/>
       <c r="B10" s="10" t="n"/>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n"/>
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n"/>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="10" t="n"/>
       <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n"/>
       <c r="B14" s="10" t="n"/>
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="n"/>
       <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
       <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n"/>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
       <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n"/>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n"/>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n"/>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n"/>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n"/>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n"/>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n"/>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="10" t="n"/>
       <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n"/>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n"/>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="10" t="n"/>
       <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n"/>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n"/>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="10" t="n"/>
       <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n"/>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n"/>
       <c r="B45" s="10" t="n"/>
       <c r="C45" s="10" t="n"/>
       <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n"/>
       <c r="B46" s="10" t="n"/>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n"/>
       <c r="B47" s="10" t="n"/>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n"/>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n"/>
       <c r="B49" s="10" t="n"/>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n"/>
       <c r="B50" s="10" t="n"/>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n"/>
       <c r="B51" s="10" t="n"/>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n"/>
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="10" t="n"/>
       <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n"/>
       <c r="B53" s="10" t="n"/>
       <c r="C53" s="10" t="n"/>
       <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n"/>
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n"/>
       <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n"/>
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n"/>
       <c r="B57" s="10" t="n"/>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n"/>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n"/>
       <c r="B59" s="10" t="n"/>
       <c r="C59" s="10" t="n"/>
       <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3899,14 +3958,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3922,15 +3980,10 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>bucket</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>bucket</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -3943,18 +3996,15 @@
       <c r="B2" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>3년 이상</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>3년 이상</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>← 이 줄은 예시입니다. CSV로 저장하기 전에 2행 전체를 지우세요.</t>
         </is>
@@ -3965,406 +4015,346 @@
       <c r="B3" s="10" t="n"/>
       <c r="C3" s="10" t="n"/>
       <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="n"/>
       <c r="B4" s="10" t="n"/>
       <c r="C4" s="10" t="n"/>
       <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="n"/>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="10" t="n"/>
       <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n"/>
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n"/>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n"/>
       <c r="B10" s="10" t="n"/>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n"/>
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n"/>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="10" t="n"/>
       <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n"/>
       <c r="B14" s="10" t="n"/>
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="n"/>
       <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
       <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n"/>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
       <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n"/>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n"/>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n"/>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n"/>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n"/>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n"/>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n"/>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="10" t="n"/>
       <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n"/>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n"/>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="10" t="n"/>
       <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n"/>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n"/>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="10" t="n"/>
       <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n"/>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n"/>
       <c r="B45" s="10" t="n"/>
       <c r="C45" s="10" t="n"/>
       <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n"/>
       <c r="B46" s="10" t="n"/>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n"/>
       <c r="B47" s="10" t="n"/>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="10" t="n"/>
-      <c r="E47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n"/>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n"/>
       <c r="B49" s="10" t="n"/>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n"/>
       <c r="B50" s="10" t="n"/>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n"/>
       <c r="B51" s="10" t="n"/>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="10" t="n"/>
-      <c r="E51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n"/>
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="10" t="n"/>
       <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n"/>
       <c r="B53" s="10" t="n"/>
       <c r="C53" s="10" t="n"/>
       <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n"/>
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n"/>
       <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="10" t="n"/>
-      <c r="E55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n"/>
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="10" t="n"/>
-      <c r="E56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n"/>
       <c r="B57" s="10" t="n"/>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n"/>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n"/>
       <c r="B59" s="10" t="n"/>
       <c r="C59" s="10" t="n"/>
       <c r="D59" s="10" t="n"/>
-      <c r="E59" s="10" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="1">
     <dataValidation sqref="C3:C200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값" error="조견표 시트의 값 중에서 골라 주세요." type="list">
-      <formula1>"1,2,3,4"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D3:D200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값" error="조견표 시트의 값 중에서 골라 주세요." type="list">
       <formula1>"3년 이상,1~3년,6개월~1년,6개월 미만"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4385,8 +4375,8 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4407,7 +4397,7 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>bucket</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -4428,10 +4418,8 @@
           <t>개발</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>30h+</t>
-        </is>
+      <c r="D2" s="8" t="n">
+        <v>34</v>
       </c>
       <c r="E2" s="8" t="n">
         <v>1</v>
@@ -4842,11 +4830,6 @@
       <c r="E59" s="10" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="D3:D200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값" error="조견표 시트의 값 중에서 골라 주세요." type="list">
-      <formula1>"0h,1-10,11-20,21-30,30h+"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -6740,7 +6723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="104" customWidth="1" min="1" max="1"/>
@@ -6760,6 +6743,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -6788,41 +6772,43 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>영업_경로 · stage / sort_order</t>
+          <t>영업_경로 · stage</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>문의(1)는 넣지 않습니다. stage 글자와 sort_order 숫자가 짝이 맞아야 합니다.</t>
+          <t>문의는 넣지 않습니다. 마케팅 전환 수에서 자동으로 계산됩니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    견적 = 2</t>
+          <t xml:space="preserve">    견적</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    협상 = 3</t>
+          <t xml:space="preserve">    협상</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    계약 = 4</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">    계약</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
@@ -6851,6 +6837,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -6886,6 +6873,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -6914,10 +6902,11 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>인사_근속 · bucket / sort_order</t>
+          <t>인사_근속 · bucket</t>
         </is>
       </c>
     </row>
@@ -6931,80 +6920,83 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3년 이상 = 1</t>
+          <t xml:space="preserve">    3년 이상</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1~3년 = 2</t>
+          <t xml:space="preserve">    1~3년</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6개월~1년 = 3</t>
+          <t xml:space="preserve">    6개월~1년</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6개월 미만 = 4</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">    6개월 미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>인사_초과근무 · bucket</t>
+          <t>인사_초과근무 · hours</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>영문 h 와 하이픈(-)을 그대로 씁니다. 인원이 0명인 칸은 아예 넣지 않아도 됩니다.</t>
+          <t>구간을 고르지 않고 실제 시간을 숫자로 씁니다. 구간은 화면에서 자동으로 나뉩니다.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    0h</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    0시간   → 0h 구간</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1-10</t>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1~10시간 → 1-10 구간</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    11-20</t>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    11~20시간 → 11-20 구간</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    21-30</t>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    21~30시간 → 21-30 구간</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    30h+</t>
-        </is>
-      </c>
-    </row>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    31시간 이상 → 30h+ 구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
@@ -7047,10 +7039,26 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
           <t>이름이 달라지면 대시보드가 다른 항목으로 인식합니다. 「네이버검색」과 「네이버 검색」은 서로 다른 채널이 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>※ 순서를 나타내는 번호(sort_order)는 넣지 않습니다. 글자만 넣으면 시스템이 알아서 순서를 매깁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>※ 코호트도 몇 달째인지 세지 않습니다. 가입한 연·월과 확인하는 연·월을 각각 쓰면 됩니다.</t>
         </is>
       </c>
     </row>
@@ -7535,17 +7543,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7566,25 +7573,20 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>count</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>won_amount</t>
         </is>
@@ -7602,24 +7604,21 @@
           <t>소개·추천</t>
         </is>
       </c>
-      <c r="D2" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>계약</t>
         </is>
       </c>
+      <c r="E2" s="8" t="n">
+        <v>59</v>
+      </c>
       <c r="F2" s="8" t="n">
-        <v>59</v>
+        <v>3162</v>
       </c>
       <c r="G2" s="8" t="n">
         <v>3162</v>
       </c>
-      <c r="H2" s="8" t="n">
-        <v>3162</v>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>← 이 줄은 예시입니다. CSV로 저장하기 전에 2행 전체를 지우세요.</t>
         </is>
@@ -7633,7 +7632,6 @@
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="n"/>
@@ -7643,7 +7641,6 @@
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="n"/>
@@ -7653,7 +7650,6 @@
       <c r="E5" s="10" t="n"/>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n"/>
-      <c r="H5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n"/>
@@ -7663,7 +7659,6 @@
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n"/>
@@ -7673,7 +7668,6 @@
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n"/>
@@ -7683,7 +7677,6 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n"/>
@@ -7693,7 +7686,6 @@
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n"/>
@@ -7703,7 +7695,6 @@
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="10" t="n"/>
       <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n"/>
@@ -7713,7 +7704,6 @@
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n"/>
@@ -7723,7 +7713,6 @@
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n"/>
@@ -7733,7 +7722,6 @@
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n"/>
@@ -7743,7 +7731,6 @@
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="10" t="n"/>
       <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n"/>
@@ -7753,7 +7740,6 @@
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
       <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n"/>
@@ -7763,7 +7749,6 @@
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n"/>
@@ -7773,7 +7758,6 @@
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
@@ -7783,7 +7767,6 @@
       <c r="E18" s="10" t="n"/>
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n"/>
@@ -7793,7 +7776,6 @@
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n"/>
@@ -7803,7 +7785,6 @@
       <c r="E20" s="10" t="n"/>
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n"/>
@@ -7813,7 +7794,6 @@
       <c r="E21" s="10" t="n"/>
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n"/>
@@ -7823,7 +7803,6 @@
       <c r="E22" s="10" t="n"/>
       <c r="F22" s="10" t="n"/>
       <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n"/>
@@ -7833,7 +7812,6 @@
       <c r="E23" s="10" t="n"/>
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
-      <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n"/>
@@ -7843,7 +7821,6 @@
       <c r="E24" s="10" t="n"/>
       <c r="F24" s="10" t="n"/>
       <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n"/>
@@ -7853,7 +7830,6 @@
       <c r="E25" s="10" t="n"/>
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n"/>
@@ -7863,7 +7839,6 @@
       <c r="E26" s="10" t="n"/>
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="10" t="n"/>
-      <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n"/>
@@ -7873,7 +7848,6 @@
       <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n"/>
@@ -7883,7 +7857,6 @@
       <c r="E28" s="10" t="n"/>
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n"/>
@@ -7893,7 +7866,6 @@
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n"/>
@@ -7903,7 +7875,6 @@
       <c r="E30" s="10" t="n"/>
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n"/>
@@ -7913,7 +7884,6 @@
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n"/>
@@ -7923,7 +7893,6 @@
       <c r="E32" s="10" t="n"/>
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n"/>
@@ -7933,7 +7902,6 @@
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n"/>
@@ -7943,7 +7911,6 @@
       <c r="E34" s="10" t="n"/>
       <c r="F34" s="10" t="n"/>
       <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n"/>
@@ -7953,7 +7920,6 @@
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n"/>
@@ -7963,7 +7929,6 @@
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
-      <c r="H36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n"/>
@@ -7973,7 +7938,6 @@
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n"/>
@@ -7983,7 +7947,6 @@
       <c r="E38" s="10" t="n"/>
       <c r="F38" s="10" t="n"/>
       <c r="G38" s="10" t="n"/>
-      <c r="H38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n"/>
@@ -7993,7 +7956,6 @@
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
-      <c r="H39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n"/>
@@ -8003,7 +7965,6 @@
       <c r="E40" s="10" t="n"/>
       <c r="F40" s="10" t="n"/>
       <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n"/>
@@ -8013,7 +7974,6 @@
       <c r="E41" s="10" t="n"/>
       <c r="F41" s="10" t="n"/>
       <c r="G41" s="10" t="n"/>
-      <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n"/>
@@ -8023,7 +7983,6 @@
       <c r="E42" s="10" t="n"/>
       <c r="F42" s="10" t="n"/>
       <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n"/>
@@ -8033,7 +7992,6 @@
       <c r="E43" s="10" t="n"/>
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
-      <c r="H43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n"/>
@@ -8043,7 +8001,6 @@
       <c r="E44" s="10" t="n"/>
       <c r="F44" s="10" t="n"/>
       <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n"/>
@@ -8053,7 +8010,6 @@
       <c r="E45" s="10" t="n"/>
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
-      <c r="H45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n"/>
@@ -8063,7 +8019,6 @@
       <c r="E46" s="10" t="n"/>
       <c r="F46" s="10" t="n"/>
       <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n"/>
@@ -8073,7 +8028,6 @@
       <c r="E47" s="10" t="n"/>
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
-      <c r="H47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n"/>
@@ -8083,7 +8037,6 @@
       <c r="E48" s="10" t="n"/>
       <c r="F48" s="10" t="n"/>
       <c r="G48" s="10" t="n"/>
-      <c r="H48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n"/>
@@ -8093,7 +8046,6 @@
       <c r="E49" s="10" t="n"/>
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n"/>
@@ -8103,7 +8055,6 @@
       <c r="E50" s="10" t="n"/>
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
-      <c r="H50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n"/>
@@ -8113,7 +8064,6 @@
       <c r="E51" s="10" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
-      <c r="H51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n"/>
@@ -8123,7 +8073,6 @@
       <c r="E52" s="10" t="n"/>
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n"/>
@@ -8133,7 +8082,6 @@
       <c r="E53" s="10" t="n"/>
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
-      <c r="H53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n"/>
@@ -8143,7 +8091,6 @@
       <c r="E54" s="10" t="n"/>
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n"/>
@@ -8153,7 +8100,6 @@
       <c r="E55" s="10" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n"/>
@@ -8163,7 +8109,6 @@
       <c r="E56" s="10" t="n"/>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
-      <c r="H56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n"/>
@@ -8173,7 +8118,6 @@
       <c r="E57" s="10" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n"/>
@@ -8183,7 +8127,6 @@
       <c r="E58" s="10" t="n"/>
       <c r="F58" s="10" t="n"/>
       <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="n"/>
@@ -8193,17 +8136,13 @@
       <c r="E59" s="10" t="n"/>
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
-      <c r="H59" s="10" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="C3:C200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값" error="조견표 시트의 값 중에서 골라 주세요." type="list">
       <formula1>"소개·추천,영업 발굴"</formula1>
     </dataValidation>
     <dataValidation sqref="D3:D200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값" error="조견표 시트의 값 중에서 골라 주세요." type="list">
-      <formula1>"2,3,4"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E3:E200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="목록에 없는 값" error="조견표 시트의 값 중에서 골라 주세요." type="list">
       <formula1>"견적,협상,계약"</formula1>
     </dataValidation>
   </dataValidations>
